--- a/ROUTE_5_PATH5_COE_AIML_CSE_MECH_AUDI/PATH5_FINAL_ODK.xlsx
+++ b/ROUTE_5_PATH5_COE_AIML_CSE_MECH_AUDI/PATH5_FINAL_ODK.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -483,13 +483,14 @@
 * Next 15 teams proceed to Round 3.
 * Next 7 teams proceed to Round 4.
 * Next 2 teams proceed to Round 5.
-⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+⚠️ STRICT PROGRESSION &amp; MANDATORY RULES:
+• Read each question properly as you cannot come back to the question once you go ahead!
 • Every single question, photo upload, and code entry is strictly MANDATORY.
 • All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
 • Lowercase letters will be rejected by validation.</v>
       </c>
       <c r="D3" t="str">
-        <v>Read all rules and instructions carefully.</v>
+        <v>Read all rules and instructions carefully. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -504,7 +505,7 @@
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E4" t="str">
         <v>yes</v>
@@ -531,7 +532,7 @@
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E5" t="str">
         <v>yes</v>
@@ -558,7 +559,7 @@
 Photo upload is mandatory</v>
       </c>
       <c r="D6" t="str">
-        <v>Take a clear photo of your team at the start desk.</v>
+        <v>Take a clear photo of your team at the start desk. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E6" t="str">
         <v>yes</v>
@@ -577,10 +578,10 @@
         <v>begin_group</v>
       </c>
       <c r="B8" t="str">
-        <v>r1_coe_group</v>
+        <v>r1_group</v>
       </c>
       <c r="C8" t="str">
-        <v>ROUND 1 — OBJECT FINDING</v>
+        <v>ROUND 1</v>
       </c>
       <c r="I8" t="str">
         <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != ''</v>
@@ -591,19 +592,19 @@
         <v>note</v>
       </c>
       <c r="B9" t="str">
-        <v>r1_coe_intro</v>
+        <v>r1_intro</v>
       </c>
       <c r="C9" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 1: 🧩 OBJECT FINDING
+        <v xml:space="preserve">📍 ROUND 1
 Instructions:
-1. Search the location to find the designated COE board/object.
+1. Search the location to find the designated board/object.
 2. Take a mandatory photo of the object.
 3. Show the object/photo to the nearby Luminus volunteer.
 4. Enter the verification code given by the volunteer.
 Enter code in caps</v>
       </c>
       <c r="D9" t="str">
-        <v>Find the COE Board object, take photo, and ask volunteer for code.</v>
+        <v>Find the object, take photo, and ask volunteer for code. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -611,14 +612,14 @@
         <v>image</v>
       </c>
       <c r="B10" t="str">
-        <v>r1_coe_photo</v>
+        <v>r1_photo</v>
       </c>
       <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered COE Board Object (MANDATORY)
+        <v xml:space="preserve">📸 Upload Photo of Discovered Object (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D10" t="str">
-        <v>Take a clear photo of the discovered COE Board object.</v>
+        <v>Take a clear photo of the discovered object. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E10" t="str">
         <v>yes</v>
@@ -632,14 +633,14 @@
         <v>text</v>
       </c>
       <c r="B11" t="str">
-        <v>r1_coe_code</v>
+        <v>r1_code</v>
       </c>
       <c r="C11" t="str" xml:space="preserve">
         <v xml:space="preserve">Enter Volunteer Verification Code (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E11" t="str">
         <v>yes</v>
@@ -667,10 +668,10 @@
         <v>r2_aiml_loc_group</v>
       </c>
       <c r="C13" t="str">
-        <v>ROUND 2 LOCATION CLUE</v>
+        <v>ROUND 2</v>
       </c>
       <c r="I13" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != ''</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != ''</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -678,29 +679,20 @@
         <v>note</v>
       </c>
       <c r="B14" t="str">
-        <v>r2_aiml_loc_note</v>
+        <v>r2_clue1_note</v>
       </c>
       <c r="C14" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 2 LOCATION CLUE: RIDDLE OF THE MISSING CONCEPT
+        <v xml:space="preserve">📍 ROUND 2
 Four clues describe four concepts.
-Solve each clue and take the first letter of each answer.
-Combine the four letters to discover your next location.
-Clue 1:
+Solve each clue slide-by-slide and enter the concept answer.
+At the end, you will take the first letter of each answer to deduce your next destination block!
+🧩 Riddle 1 of 4:
 "Step by step, I show the way,
 solving problems every day."
-Clue 2:
-"I connect the world without a sound,
-through wires and waves, I'm all around."
-Clue 3:
-"I learn from data, again and again,
-getting smarter with every gain."
-Clue 4:
-"I'm the code you write, line by line,
-Python or Java, the choice is fine."
 Enter code in caps</v>
       </c>
       <c r="D14" t="str">
-        <v>Take the first letter of each answer and combine them.</v>
+        <v>Solve Riddle 1 for the first concept. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -708,26 +700,26 @@
         <v>text</v>
       </c>
       <c r="B15" t="str">
-        <v>r2_aiml_loc_answer</v>
+        <v>r2_clue1_answer</v>
       </c>
       <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter your 4-letter combined destination location: (MANDATORY)
+        <v xml:space="preserve">Enter Concept 1 Answer: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D15" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E15" t="str">
         <v>yes</v>
       </c>
       <c r="F15" t="str">
-        <v>❌ Destination location is mandatory.</v>
+        <v>❌ Riddle 1 answer is mandatory.</v>
       </c>
       <c r="G15" t="str">
-        <v>regex(., '^[A-Z0-9\/&amp; ]+$') and (normalize-space(.) = 'AIML' or normalize-space(.) = 'AI ML' or normalize-space(.) = 'AIML BLOCK' or normalize-space(.) = 'AI/ML' or normalize-space(.) = 'AI &amp; ML')</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'ALGORITHMS')</v>
       </c>
       <c r="H15" t="str">
-        <v>❌ Incorrect. Solve all four clues and take the first letter of each answer.</v>
+        <v>❌ Incorrect answer. Solve Riddle 1 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -735,17 +727,16 @@
         <v>note</v>
       </c>
       <c r="B16" t="str">
-        <v>r2_aiml_proceed_note</v>
+        <v>r2_clue2_note</v>
       </c>
       <c r="C16" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 Correct! Proceed to the location identified by your answer and enter the START CODE provided there.
+        <v xml:space="preserve">🧩 Riddle 2 of 4:
+"I connect the world without a sound,
+through wires and waves, I'm all around."
 Enter code in caps</v>
       </c>
       <c r="D16" t="str">
-        <v>Proceed to the location and ask volunteer for start code.</v>
-      </c>
-      <c r="I16" t="str">
-        <v>normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML'</v>
+        <v>Solve Riddle 2 for the second concept. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -753,48 +744,70 @@
         <v>text</v>
       </c>
       <c r="B17" t="str">
-        <v>r2_aiml_start_code</v>
+        <v>r2_clue2_answer</v>
       </c>
       <c r="C17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
+        <v xml:space="preserve">Enter Concept 2 Answer: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D17" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E17" t="str">
         <v>yes</v>
       </c>
       <c r="F17" t="str">
-        <v>❌ START CODE is mandatory.</v>
+        <v>❌ Riddle 2 answer is mandatory.</v>
       </c>
       <c r="G17" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'AIML-START'</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'INTERNET'</v>
       </c>
       <c r="H17" t="str">
-        <v>❌ Incorrect START CODE. Check the code at your current location and enter it exactly as provided.</v>
-      </c>
-      <c r="I17" t="str">
-        <v>normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML'</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>note</v>
+      </c>
+      <c r="B18" t="str">
+        <v>r2_clue3_note</v>
+      </c>
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧩 Riddle 3 of 4:
+"I learn from data, again and again,
+getting smarter with every gain."
+Enter code in caps</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Solve Riddle 3 for the third concept. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
-        <v>begin_group</v>
+        <v>text</v>
       </c>
       <c r="B19" t="str">
-        <v>r2_aiml_challenge_group</v>
-      </c>
-      <c r="C19" t="str">
-        <v>ROUND 2 — AIML CHALLENGES</v>
-      </c>
-      <c r="I19" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START'</v>
+        <v>r2_clue3_answer</v>
+      </c>
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Concept 3 Answer: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D19" t="str">
+        <v>ENTER ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E19" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F19" t="str">
+        <v>❌ Riddle 3 answer is mandatory.</v>
+      </c>
+      <c r="G19" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MODEL' or normalize-space(.) = 'MODELS' or normalize-space(.) = 'MACHINE LEARNING')</v>
+      </c>
+      <c r="H19" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 3 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
@@ -802,10 +815,162 @@
         <v>note</v>
       </c>
       <c r="B20" t="str">
+        <v>r2_clue4_note</v>
+      </c>
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧩 Riddle 4 of 4:
+"I'm the code you write, line by line,
+Python or Java, the choice is fine."
+Enter code in caps</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Solve Riddle 4 for the fourth concept. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>text</v>
+      </c>
+      <c r="B21" t="str">
+        <v>r2_clue4_answer</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Concept 4 Answer: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D21" t="str">
+        <v>ENTER ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E21" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F21" t="str">
+        <v>❌ Riddle 4 answer is mandatory.</v>
+      </c>
+      <c r="G21" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'LANGUAGE' or normalize-space(.) = 'LANGUAGES' or normalize-space(.) = 'PROGRAMMING LANGUAGE')</v>
+      </c>
+      <c r="H21" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 4 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>note</v>
+      </c>
+      <c r="B22" t="str">
+        <v>r2_aiml_deduce_note</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧠 DEDUCE THE NEXT DESTINATION BLOCK!
+Now, recall and take the FIRST LETTER of each of the 4 concept answers you just solved in sequence.
+Combine those four initial letters to deduce and reveal your next destination block!
+Enter code in caps</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Deduce the 4-letter block name from your answers. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>text</v>
+      </c>
+      <c r="B23" t="str">
+        <v>r2_aiml_loc_answer</v>
+      </c>
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter your 4-letter combined destination location: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D23" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E23" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F23" t="str">
+        <v>❌ Destination location is mandatory.</v>
+      </c>
+      <c r="G23" t="str">
+        <v>regex(., '^[A-Z0-9\/&amp; ]+$') and (normalize-space(.) = 'AIML' or normalize-space(.) = 'AI ML' or normalize-space(.) = 'AIML BLOCK' or normalize-space(.) = 'AI/ML' or normalize-space(.) = 'AI &amp; ML')</v>
+      </c>
+      <c r="H23" t="str">
+        <v>❌ Incorrect. Take the first letter of each concept to find the block name.</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>note</v>
+      </c>
+      <c r="B24" t="str">
+        <v>r2_aiml_proceed_note</v>
+      </c>
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Proceed to the destination block and report to the station volunteer to begin your challenge.
+Enter code in caps</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Proceed to the station. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="I24" t="str">
+        <v>normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML'</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B26" t="str">
+        <v>r2_aiml_challenge_group</v>
+      </c>
+      <c r="C26" t="str">
+        <v>ROUND 2</v>
+      </c>
+      <c r="I26" t="str">
+        <v>normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML'</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>text</v>
+      </c>
+      <c r="B27" t="str">
+        <v>r2_aiml_start_code</v>
+      </c>
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Challenge START CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D27" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E27" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F27" t="str">
+        <v>❌ START CODE is mandatory.</v>
+      </c>
+      <c r="G27" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'GEMMA-V05'</v>
+      </c>
+      <c r="H27" t="str">
+        <v>❌ Incorrect START CODE. Enter GEMMA-V05 in CAPS provided by the volunteer.</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>note</v>
+      </c>
+      <c r="B28" t="str">
         <v>r2_aiml_prompt_rules_note</v>
       </c>
-      <c r="C20" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎨 AIML CHALLENGE: REVERSE IMAGE PROMPTING
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎨 ROUND 2
 Event Format:
 • One lab system will be provided per team.
 • Images will be displayed for 10 seconds each in a slideshow.
@@ -818,177 +983,115 @@
 • Volunteers will come to your system and verify your generated images directly.
 Enter code in caps</v>
       </c>
-      <c r="D20" t="str">
-        <v>Follow lab instructions and volunteer guidance.</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>select_one challenge_status_list</v>
-      </c>
-      <c r="B21" t="str">
-        <v>r2_aiml_challenge_status</v>
-      </c>
-      <c r="C21" t="str">
-        <v>AIML Image Prompting Challenge Status (MANDATORY)</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Select PASSED once verified by station volunteers.</v>
-      </c>
-      <c r="E21" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F21" t="str">
-        <v>❌ Challenge status selection is mandatory.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>note</v>
-      </c>
-      <c r="B22" t="str">
-        <v>r2_aiml_not_passed_note</v>
-      </c>
-      <c r="C22" t="str">
-        <v>⚠️ Challenge not cleared. Follow the organizer's instructions before continuing.</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Complete the image generation prompt challenge.</v>
-      </c>
-      <c r="I22" t="str">
-        <v>${r2_aiml_challenge_status} = 'not_passed'</v>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str">
-        <v>note</v>
-      </c>
-      <c r="B23" t="str">
-        <v>r2_aiml_passed_note</v>
-      </c>
-      <c r="C23" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎉 Challenge cleared. Enter the code provided by the organizer.
-Enter code in caps</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Ask volunteer for clearance code.</v>
-      </c>
-      <c r="I23" t="str">
-        <v>${r2_aiml_challenge_status} = 'passed'</v>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24" t="str">
-        <v>image</v>
-      </c>
-      <c r="B24" t="str">
-        <v>r2_aiml_photo</v>
-      </c>
-      <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Generated Images / Station (MANDATORY)
-Photo upload is mandatory</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Take a clear photo of your team's generated images on the lab screen.</v>
-      </c>
-      <c r="E24" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F24" t="str">
-        <v>❌ Station verification photo is mandatory.</v>
-      </c>
-      <c r="I24" t="str">
-        <v>${r2_aiml_challenge_status} = 'passed'</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str">
-        <v>text</v>
-      </c>
-      <c r="B25" t="str">
-        <v>r2_aiml_code1</v>
-      </c>
-      <c r="C25" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code 1 (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D25" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E25" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F25" t="str">
-        <v>❌ Volunteer clearance code is mandatory.</v>
-      </c>
-      <c r="G25" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'GEMMA-V05'</v>
-      </c>
-      <c r="H25" t="str">
-        <v>❌ Incorrect code. Check the code obtained after completing the challenge.</v>
-      </c>
-      <c r="I25" t="str">
-        <v>${r2_aiml_challenge_status} = 'passed'</v>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26" t="str">
-        <v>text</v>
-      </c>
-      <c r="B26" t="str">
-        <v>r2_aiml_end_code</v>
-      </c>
-      <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Station Finish Code 2 from Volunteer (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D26" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E26" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F26" t="str">
-        <v>❌ Station finish code is mandatory.</v>
-      </c>
-      <c r="G26" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'OLLAMA-V05' or normalize-space(.) = 'OLLAMA-v05')</v>
-      </c>
-      <c r="H26" t="str">
-        <v>❌ Incorrect finish code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
-      </c>
-      <c r="I26" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05'</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B28" t="str">
-        <v>r3_cse_loc_group</v>
-      </c>
-      <c r="C28" t="str">
-        <v>ROUND 3 LOCATION CLUE</v>
+      <c r="D28" t="str">
+        <v>Follow lab instructions and volunteer guidance. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="I28" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != ''</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05'</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>note</v>
+        <v>image</v>
       </c>
       <c r="B29" t="str">
+        <v>r2_aiml_photo1</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo 1 of Generated Images / Station Screen (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Take a clear photo of your team's generated images on the lab screen. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E29" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F29" t="str">
+        <v>❌ Station verification photo 1 is mandatory.</v>
+      </c>
+      <c r="I29" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05'</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>image</v>
+      </c>
+      <c r="B30" t="str">
+        <v>r2_aiml_photo2</v>
+      </c>
+      <c r="C30" t="str">
+        <v>📸 Upload Photo 2 of Additional Generated Images (OPTIONAL)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Optional: Upload a second photo of your team's generated images. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E30" t="str">
+        <v>no</v>
+      </c>
+      <c r="I30" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05'</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>text</v>
+      </c>
+      <c r="B31" t="str">
+        <v>r2_aiml_end_code</v>
+      </c>
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer FINAL Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D31" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E31" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F31" t="str">
+        <v>❌ Station final clearance code is mandatory.</v>
+      </c>
+      <c r="G31" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'OLLAMA-V05' or normalize-space(.) = 'OLLAMA-v05')</v>
+      </c>
+      <c r="H31" t="str">
+        <v>❌ Incorrect final code. Enter OLLAMA-V05 in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I31" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05'</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B33" t="str">
+        <v>r3_cse_loc_group</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ROUND 3</v>
+      </c>
+      <c r="I33" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != ''</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>note</v>
+      </c>
+      <c r="B34" t="str">
         <v>r3_cse_math_note</v>
       </c>
-      <c r="C29" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE: MATHEMATICAL CODE
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 3
 Three numbers are hidden inside the equations.
 Solve each equation.
 Then use the alphabet as your key:
@@ -998,136 +1101,53 @@
 (1 + 2) — (20 − 1) — (10 ÷ 2)
 Enter code in caps</v>
       </c>
-      <c r="D29" t="str">
-        <v>Solve each equation and map the 3 numbers to letters A=1 to Z=26.</v>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
+      <c r="D34" t="str">
+        <v>Solve each equation and map the 3 numbers to letters A=1 to Z=26. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
         <v>text</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B35" t="str">
         <v>r3_cse_loc_answer</v>
       </c>
-      <c r="C30" t="str" xml:space="preserve">
+      <c r="C35" t="str" xml:space="preserve">
         <v xml:space="preserve">Enter your uncovered 3-letter destination location: (MANDATORY)
 Enter code in caps</v>
       </c>
-      <c r="D30" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E30" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F30" t="str">
+      <c r="D35" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E35" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F35" t="str">
         <v>❌ Destination location is mandatory.</v>
       </c>
-      <c r="G30" t="str">
+      <c r="G35" t="str">
         <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'CSE' or normalize-space(.) = 'CSE BLOCK')</v>
       </c>
-      <c r="H30" t="str">
+      <c r="H35" t="str">
         <v>❌ Incorrect. Solve all three equations first, then convert the resulting numbers using A=1, B=2, C=3...Z=26.</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str">
-        <v>note</v>
-      </c>
-      <c r="B31" t="str">
-        <v>r3_cse_proceed_note</v>
-      </c>
-      <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 Correct! You have uncovered the three-letter code. Proceed to the location and look for the QR challenge.
-Enter code in caps</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Proceed to the location for the QR hunt.</v>
-      </c>
-      <c r="I31" t="str">
-        <v>normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK'</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B33" t="str">
-        <v>r3_cse_qr_group</v>
-      </c>
-      <c r="C33" t="str">
-        <v>ROUND 3 — QR HUNT</v>
-      </c>
-      <c r="I33" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK')</v>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34" t="str">
-        <v>note</v>
-      </c>
-      <c r="B34" t="str">
-        <v>r3_cse_qr_note</v>
-      </c>
-      <c r="C34" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3: QR HUNT
-Find the designated QR code at this location and scan it.
-Follow the instructions provided by the QR challenge.
-Enter code in caps</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Locate and scan the hidden QR code.</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>barcode</v>
-      </c>
-      <c r="B35" t="str">
-        <v>r3_cse_qr_scan</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Scan Discovered QR Code (MANDATORY)</v>
-      </c>
-      <c r="D35" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E35" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F35" t="str">
-        <v>❌ QR code scanning is mandatory.</v>
-      </c>
-      <c r="G35" t="str">
-        <v>normalize-space(.) = 'PETER_PARKER'</v>
-      </c>
-      <c r="H35" t="str">
-        <v>❌ Incorrect code. Continue the QR hunt and check the code carefully.</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>image</v>
+        <v>note</v>
       </c>
       <c r="B36" t="str">
-        <v>r3_cse_qr_photo</v>
+        <v>r3_cse_proceed_note</v>
       </c>
       <c r="C36" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered QR Code / Station (MANDATORY)
-Photo upload is mandatory</v>
+        <v xml:space="preserve">🏃 Correct! You have uncovered the three-letter code. Proceed to the location and look for the QR challenge.
+Enter code in caps</v>
       </c>
       <c r="D36" t="str">
-        <v>Take a clear photo of the discovered QR code location.</v>
-      </c>
-      <c r="E36" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F36" t="str">
-        <v>❌ Station photo upload is mandatory.</v>
+        <v>Proceed to the location for the QR hunt. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="I36" t="str">
+        <v>normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK'</v>
       </c>
     </row>
     <row r="37">
@@ -1140,13 +1160,13 @@
         <v>begin_group</v>
       </c>
       <c r="B38" t="str">
-        <v>r4_mech_loc_group</v>
+        <v>r3_cse_qr_group</v>
       </c>
       <c r="C38" t="str">
-        <v>ROUND 4 LOCATION CLUE</v>
+        <v>ROUND 3</v>
       </c>
       <c r="I38" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != ''</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK')</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
@@ -1154,291 +1174,296 @@
         <v>note</v>
       </c>
       <c r="B39" t="str">
+        <v>r3_cse_qr_note</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 3
+Find the designated QR code at this location and scan it.
+Follow the instructions provided by the QR challenge.
+Enter code in caps</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Locate and scan the hidden QR code. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>barcode</v>
+      </c>
+      <c r="B40" t="str">
+        <v>r3_cse_qr_scan</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Scan Discovered QR Code (MANDATORY)</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Scan the QR code found at the location. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E40" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F40" t="str">
+        <v>❌ QR code scanning is mandatory.</v>
+      </c>
+      <c r="G40" t="str">
+        <v>normalize-space(.) = 'PETER_PARKER' or contains(., 'PETER_PARKER')</v>
+      </c>
+      <c r="H40" t="str">
+        <v>❌ Incorrect code. Continue the QR hunt and check the code carefully.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B42" t="str">
+        <v>r4_mech_loc_group</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ROUND 4</v>
+      </c>
+      <c r="I42" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER'))</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>note</v>
+      </c>
+      <c r="B43" t="str">
         <v>r4_mech_piece_note</v>
       </c>
-      <c r="C39" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 4 LOCATION CLUE: PIECE-BY-PIECE
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 4
 Piece by piece, an image has been hidden from you.
 Study the available pieces in the image attached below and determine what place or object they form.
 Your answer will help identify your next location.
 Enter code in caps</v>
       </c>
-      <c r="D39" t="str">
-        <v>Examine the image pieces to identify the destination.</v>
-      </c>
-      <c r="J39" t="str">
+      <c r="D43" t="str">
+        <v>Examine the image pieces to identify the destination. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="J43" t="str">
         <v>badminton court.jpeg</v>
       </c>
     </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
         <v>text</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B44" t="str">
         <v>r4_mech_loc_answer</v>
       </c>
-      <c r="C40" t="str" xml:space="preserve">
+      <c r="C44" t="str" xml:space="preserve">
         <v xml:space="preserve">Enter the location/object identified from the photograph pieces: (MANDATORY)
 Enter code in caps</v>
       </c>
-      <c r="D40" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E40" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F40" t="str">
+      <c r="D44" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E44" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F44" t="str">
         <v>❌ Location answer is mandatory.</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G44" t="str">
         <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MECH' or normalize-space(.) = 'MECH BLOCK' or normalize-space(.) = 'MECHANICAL' or normalize-space(.) = 'BADMINTON COURT')</v>
       </c>
-      <c r="H40" t="str">
+      <c r="H44" t="str">
         <v>❌ Incorrect. Examine the image pieces carefully to identify the campus location.</v>
       </c>
-      <c r="J40" t="str">
+      <c r="J44" t="str">
         <v>badminton court.jpeg</v>
       </c>
     </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41" t="str">
-        <v>note</v>
-      </c>
-      <c r="B41" t="str">
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>note</v>
+      </c>
+      <c r="B45" t="str">
         <v>r4_mech_proceed_note</v>
       </c>
-      <c r="C41" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 Correct! Proceed to the location identified by your answer and look for the physical challenge.
-Enter code in caps</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Proceed to the location and ask volunteer for start code.</v>
-      </c>
-      <c r="I41" t="str">
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Proceed to the destination block and report to the station volunteer for your physical challenge.
+Enter code in caps</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Proceed to the station. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="I45" t="str">
         <v>normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT'</v>
       </c>
     </row>
-    <row r="42" xml:space="preserve">
-      <c r="A42" t="str">
-        <v>text</v>
-      </c>
-      <c r="B42" t="str">
-        <v>r4_mech_start_code</v>
-      </c>
-      <c r="C42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D42" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E42" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F42" t="str">
-        <v>❌ START CODE is mandatory.</v>
-      </c>
-      <c r="G42" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'PIECE-START' or normalize-space(.) = 'PIECE_START')</v>
-      </c>
-      <c r="H42" t="str">
-        <v>❌ Incorrect START CODE. Enter PIECE-START in CAPS provided by the volunteer.</v>
-      </c>
-      <c r="I42" t="str">
-        <v>normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT'</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
+    <row r="46">
+      <c r="A46" t="str">
         <v>end_group</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B44" t="str">
-        <v>r4_mech_phy_group</v>
-      </c>
-      <c r="C44" t="str">
-        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
-      </c>
-      <c r="I44" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START')</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>select_one yes_no_list</v>
-      </c>
-      <c r="B45" t="str">
-        <v>r4_enable_optional_piece</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Enable Piece-by-Piece Station Challenge? (Organizer Option)</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Select YES to record station challenge or NO to proceed directly to physical challenge.</v>
-      </c>
-      <c r="E45" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F45" t="str">
-        <v>❌ Selection is mandatory.</v>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46" t="str">
-        <v>note</v>
-      </c>
-      <c r="B46" t="str">
-        <v>r4_mech_phy_note</v>
-      </c>
-      <c r="C46" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE
-Report to the station and complete the physical challenge under volunteer supervision.
-Enter code in caps</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Complete physical challenge with volunteer.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>select_one challenge_status_list</v>
+        <v>begin_group</v>
       </c>
       <c r="B47" t="str">
-        <v>r4_mech_status</v>
+        <v>r4_mech_phy_group</v>
       </c>
       <c r="C47" t="str">
-        <v>Physical Challenge Status (MANDATORY)</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Select PASSED once completed with volunteer.</v>
-      </c>
-      <c r="E47" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F47" t="str">
-        <v>❌ Challenge status selection is mandatory.</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>ROUND 4</v>
+      </c>
+      <c r="I47" t="str">
+        <v>normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT'</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B48" t="str">
-        <v>r4_mech_not_passed_note</v>
-      </c>
-      <c r="C48" t="str">
-        <v>⚠️ Please follow the organizer's instructions before continuing.</v>
+        <v>r4_mech_start_code</v>
+      </c>
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Physical Challenge START CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D48" t="str">
-        <v>Complete the physical challenge as instructed.</v>
-      </c>
-      <c r="I48" t="str">
-        <v>${r4_mech_status} = 'not_passed'</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E48" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F48" t="str">
+        <v>❌ START CODE is mandatory.</v>
+      </c>
+      <c r="G48" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'PIECE-START' or normalize-space(.) = 'PIECE_START')</v>
+      </c>
+      <c r="H48" t="str">
+        <v>❌ Incorrect START CODE. Enter PIECE-START in CAPS provided by the volunteer.</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str">
+        <v>note</v>
+      </c>
+      <c r="B49" t="str">
+        <v>r4_mech_phy_note</v>
+      </c>
+      <c r="C49" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 4
+Report to the station and complete the physical challenge under volunteer supervision.
+Once completed, take a team photo and ask the volunteer for the END CODE.
+Enter code in caps</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Complete physical challenge with volunteer. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="I49" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START')</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
         <v>image</v>
       </c>
-      <c r="B49" t="str">
+      <c r="B50" t="str">
         <v>r4_mech_phy_photo</v>
       </c>
-      <c r="C49" t="str" xml:space="preserve">
+      <c r="C50" t="str" xml:space="preserve">
         <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion (MANDATORY)
 Photo upload is mandatory</v>
       </c>
-      <c r="D49" t="str">
-        <v>Take a clear photo of your team completing the physical challenge.</v>
-      </c>
-      <c r="E49" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F49" t="str">
+      <c r="D50" t="str">
+        <v>Take a clear photo of your team completing the physical challenge. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E50" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F50" t="str">
         <v>❌ Challenge photo upload is mandatory.</v>
       </c>
-      <c r="I49" t="str">
-        <v>${r4_mech_status} = 'passed'</v>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50" t="str">
+      <c r="I50" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START')</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
         <v>text</v>
       </c>
-      <c r="B50" t="str">
+      <c r="B51" t="str">
         <v>r4_mech_phy_code</v>
       </c>
-      <c r="C50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Completion Code (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D50" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E50" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F50" t="str">
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer END / Completion Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D51" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E51" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F51" t="str">
         <v>❌ Volunteer completion code is mandatory.</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G51" t="str">
         <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'PIECE-BYE' or normalize-space(.) = 'PIECE-BYE---' or normalize-space(.) = 'PIECE_BYE')</v>
       </c>
-      <c r="H50" t="str">
+      <c r="H51" t="str">
         <v>❌ Incorrect code. Enter PIECE-BYE in CAPS provided by the volunteer.</v>
       </c>
-      <c r="I50" t="str">
-        <v>${r4_mech_status} = 'passed'</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>end_group</v>
+      <c r="I51" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START')</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B52" t="str">
+      <c r="B53" t="str">
         <v>final_puzzles_group</v>
       </c>
-      <c r="C52" t="str">
-        <v>FINAL ROUND</v>
-      </c>
-      <c r="I52" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and ${r4_mech_status} = 'passed' and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != ''</v>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53" t="str">
-        <v>note</v>
-      </c>
-      <c r="B53" t="str">
-        <v>final_audi_stage_intro</v>
-      </c>
-      <c r="C53" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏛️ FINAL ROUND — RIDDLES
-Solve the two final riddles to reveal the final destination!
-Enter code in caps</v>
-      </c>
-      <c r="D53" t="str">
-        <v>Solve the final riddles in CAPS.</v>
+      <c r="C53" t="str">
+        <v>ROUND 5</v>
+      </c>
+      <c r="I53" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != ''</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
       <c r="A54" t="str">
+        <v>note</v>
+      </c>
+      <c r="B54" t="str">
+        <v>final_audi_stage_intro</v>
+      </c>
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏛️ ROUND 5
+Solve the two final riddles to reveal the final destination!
+Enter code in caps</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Solve the final riddles in CAPS. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
         <v>text</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B55" t="str">
         <v>final_riddle1_answer</v>
       </c>
-      <c r="C54" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧩 AUDITORIUM RIDDLE: (MANDATORY)
-"I am empty, yet I am built for crowds.
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">"I am empty, yet I am built for crowds.
 I have a stage, but no actors of my own.
 I have countless seats, but none are meant to sleep.
 When a voice rises before me, silence falls behind me.
@@ -1446,221 +1471,164 @@
 What am I?"
 Enter code in caps</v>
       </c>
-      <c r="D54" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E54" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F54" t="str">
+      <c r="D55" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E55" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F55" t="str">
         <v>❌ Solving Riddle 1 is mandatory.</v>
       </c>
-      <c r="G54" t="str">
+      <c r="G55" t="str">
         <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'AUDITORIUM' or normalize-space(.) = 'AUDI')</v>
       </c>
-      <c r="H54" t="str">
+      <c r="H55" t="str">
         <v>❌ Incorrect answer. Solve Riddle 1 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
-    <row r="55" xml:space="preserve">
-      <c r="A55" t="str">
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
         <v>text</v>
       </c>
-      <c r="B55" t="str">
+      <c r="B56" t="str">
         <v>final_riddle2_stage_answer</v>
       </c>
-      <c r="C55" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎭 STAGE RIDDLE: (MANDATORY)
-"I am elevated above the crowd, where performers stand and spotlights shine.
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">"I am elevated above the crowd, where performers stand and spotlights shine.
 Underneath my wooden floor or behind the curtains, the ultimate secret waits.
 What am I?"
 Enter code in caps</v>
       </c>
-      <c r="D55" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E55" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F55" t="str">
+      <c r="D56" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E56" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F56" t="str">
         <v>❌ Solving Riddle 2 is mandatory.</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G56" t="str">
         <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'STAGE'</v>
       </c>
-      <c r="H55" t="str">
+      <c r="H56" t="str">
         <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
-      <c r="I55" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and ${r4_mech_status} = 'passed' and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
-      </c>
-    </row>
-    <row r="56" xml:space="preserve">
-      <c r="A56" t="str">
-        <v>note</v>
-      </c>
-      <c r="B56" t="str">
+      <c r="I56" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>note</v>
+      </c>
+      <c r="B57" t="str">
         <v>final_proceed_stage_note</v>
       </c>
-      <c r="C56" t="str" xml:space="preserve">
+      <c r="C57" t="str" xml:space="preserve">
         <v xml:space="preserve">🏃 Proceed to the final location identified!
 Solve the final puzzle at the stage, upload a photo of the completed puzzle, and get your clearance code from the Chief Judge!
 Enter code in caps</v>
       </c>
-      <c r="D56" t="str">
-        <v>Go to the stage to solve the final puzzle.</v>
-      </c>
-      <c r="I56" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and ${r4_mech_status} = 'passed' and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
-      </c>
-    </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57" t="str">
+      <c r="D57" t="str">
+        <v>Go to the stage to solve the final puzzle. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="I57" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
         <v>image</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B58" t="str">
         <v>final_solved_puzzle_photo</v>
       </c>
-      <c r="C57" t="str" xml:space="preserve">
+      <c r="C58" t="str" xml:space="preserve">
         <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle (MANDATORY)
 Photo upload is mandatory</v>
       </c>
-      <c r="D57" t="str">
-        <v>Take a clear photo of your team's completed/solved puzzle.</v>
-      </c>
-      <c r="E57" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F57" t="str">
+      <c r="D58" t="str">
+        <v>Take a clear photo of your team's completed/solved puzzle. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E58" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F58" t="str">
         <v>❌ Photo of the solved puzzle is mandatory.</v>
       </c>
-      <c r="I57" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and ${r4_mech_status} = 'passed' and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str">
-        <v>text</v>
-      </c>
-      <c r="B58" t="str">
-        <v>final_stage_volunteer_code</v>
-      </c>
-      <c r="C58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Final Volunteer Clearance Code (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D58" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E58" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F58" t="str">
-        <v>❌ Final clearance code is mandatory.</v>
-      </c>
-      <c r="G58" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'FINAL-PATH5' or normalize-space(.) = 'FINAL-PATH1' or normalize-space(.) = 'FINAL-PATH2' or normalize-space(.) = 'FINAL-PATH3' or normalize-space(.) = 'FINAL-PATH4')</v>
-      </c>
-      <c r="H58" t="str">
-        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
-      </c>
       <c r="I58" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and ${r4_mech_status} = 'passed' and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B59" t="str">
+        <v>final_stage_volunteer_code</v>
+      </c>
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Final Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D59" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E59" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F59" t="str">
+        <v>❌ Final clearance code is mandatory.</v>
+      </c>
+      <c r="G59" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'FINAL-PATH5' or normalize-space(.) = 'FINAL-PATH1' or normalize-space(.) = 'FINAL-PATH2' or normalize-space(.) = 'FINAL-PATH3' or normalize-space(.) = 'FINAL-PATH4')</v>
+      </c>
+      <c r="H59" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
+      </c>
+      <c r="I59" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
+        <v>note</v>
+      </c>
+      <c r="B60" t="str">
         <v>final_congratulations_screen</v>
       </c>
-      <c r="C59" t="str" xml:space="preserve">
+      <c r="C60" t="str" xml:space="preserve">
         <v xml:space="preserve">🎉 CONGRATULATIONS! YOU HAVE COMPLETED PATH 5!
 🏆 You have successfully entered the final clearance code!
 🔔 NOW RUN TO GO RING THE BELL TO WIN THE GAME! 🔔🏃💨</v>
       </c>
-      <c r="D59" t="str">
+      <c r="D60" t="str">
         <v>Run to ring the bell to claim victory!</v>
       </c>
-      <c r="I59" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_coe_code}) = 'YAAKE-GURU-5' and ${r1_coe_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'AIML-START' and ${r2_aiml_challenge_status} = 'passed' and normalize-space(${r2_aiml_code1}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' and ${r3_cse_qr_photo} != '' and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and ${r4_mech_status} = 'passed' and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH5' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH3' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH4') and ${final_solved_puzzle_photo} != ''</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
+      <c r="I60" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_code}) = 'YAAKE-GURU-5' and ${r1_photo} != '' and (normalize-space(${r2_aiml_loc_answer}) = 'AIML' or normalize-space(${r2_aiml_loc_answer}) = 'AI ML' or normalize-space(${r2_aiml_loc_answer}) = 'AIML BLOCK' or normalize-space(${r2_aiml_loc_answer}) = 'AI/ML' or normalize-space(${r2_aiml_loc_answer}) = 'AI &amp; ML') and normalize-space(${r2_aiml_start_code}) = 'GEMMA-V05' and (normalize-space(${r2_aiml_end_code}) = 'OLLAMA-V05' or normalize-space(${r2_aiml_end_code}) = 'OLLAMA-v05') and ${r2_aiml_photo1} != '' and (normalize-space(${r3_cse_loc_answer}) = 'CSE' or normalize-space(${r3_cse_loc_answer}) = 'CSE BLOCK') and (normalize-space(${r3_cse_qr_scan}) = 'PETER_PARKER' or contains(${r3_cse_qr_scan}, 'PETER_PARKER')) and (normalize-space(${r4_mech_loc_answer}) = 'MECH' or normalize-space(${r4_mech_loc_answer}) = 'MECH BLOCK' or normalize-space(${r4_mech_loc_answer}) = 'MECHANICAL' or normalize-space(${r4_mech_loc_answer}) = 'BADMINTON COURT') and (normalize-space(${r4_mech_start_code}) = 'PIECE-START' or normalize-space(${r4_mech_start_code}) = 'PIECE_START') and (normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE' or normalize-space(${r4_mech_phy_code}) = 'PIECE-BYE---' or normalize-space(${r4_mech_phy_code}) = 'PIECE_BYE') and ${r4_mech_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH5' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH3' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH4') and ${final_solved_puzzle_photo} != ''</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
         <v>end_group</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J61"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>list_name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>challenge_status_list</v>
-      </c>
-      <c r="B2" t="str">
-        <v>passed</v>
-      </c>
-      <c r="C2" t="str">
-        <v>PASSED</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>challenge_status_list</v>
-      </c>
-      <c r="B3" t="str">
-        <v>not_passed</v>
-      </c>
-      <c r="C3" t="str">
-        <v>NOT PASSED</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>yes_no_list</v>
-      </c>
-      <c r="B4" t="str">
-        <v>yes</v>
-      </c>
-      <c r="C4" t="str">
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>yes_no_list</v>
-      </c>
-      <c r="B5" t="str">
-        <v>no</v>
-      </c>
-      <c r="C5" t="str">
-        <v>NO</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
